--- a/templates/training_plan_template.xlsx
+++ b/templates/training_plan_template.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="51">
   <si>
     <t xml:space="preserve">Week</t>
   </si>
@@ -164,7 +164,16 @@
     <t xml:space="preserve">Optional link to a demonstration video (e.g. YouTube, MuscleWiki). Imported as a link, not embedded.</t>
   </si>
   <si>
-    <t xml:space="preserve">Note: photos and videos attached directly in the app can't be represented in a spreadsheet — only the Video URL link and text Notes round-trip through this template. Everything else (in-app media, session logs, progress history) lives only in the app itself.</t>
+    <t xml:space="preserve">Note: a photo CAN come along with this template via the 'Picture' column above — but only when you zip this spreadsheet together with the image files it names and import using 'From spreadsheet + pictures (.zip)' (Plans &gt; New plan). A plain .csv/.xlsx import by itself can't carry the image, since a spreadsheet cell can only hold text. Video URL remains a link only, not an embedded file. Session logs and progress history live only in the app itself.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Picture</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bench_press.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optional filename of a photo for this exercise, e.g. 'bench_press.jpg'. Only works when importing via 'From spreadsheet + pictures (.zip)' — zip this spreadsheet together with the image files it names (using exactly these filenames; folder structure inside the zip doesn't matter) and import that zip instead of the plain spreadsheet. The photo attaches to the resulting exercise. Leave blank for rows that don't need one.</t>
   </si>
 </sst>
 </file>
@@ -615,7 +624,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K46"/>
+  <dimension ref="A1:L46"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="7"/>
@@ -629,6 +638,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="28"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="24"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -665,6 +675,9 @@
       <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
+      <c r="L1" s="1" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="n">
@@ -698,6 +711,9 @@
         <v>16</v>
       </c>
       <c r="K2" s="3"/>
+      <c r="L2" s="3" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="n">
@@ -731,6 +747,7 @@
       <c r="K3" s="3" t="s">
         <v>19</v>
       </c>
+      <c r="L3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="n">
@@ -764,6 +781,7 @@
         <v>23</v>
       </c>
       <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="n">
@@ -797,6 +815,7 @@
         <v>29</v>
       </c>
       <c r="K5" s="3"/>
+      <c r="L5" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="n">
@@ -828,6 +847,7 @@
       </c>
       <c r="J6" s="3"/>
       <c r="K6" s="3"/>
+      <c r="L6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4"/>
@@ -841,6 +861,7 @@
       <c r="I7" s="4"/>
       <c r="J7" s="4"/>
       <c r="K7" s="4"/>
+      <c r="L7" s="4"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4"/>
@@ -854,6 +875,7 @@
       <c r="I8" s="4"/>
       <c r="J8" s="4"/>
       <c r="K8" s="4"/>
+      <c r="L8" s="4"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4"/>
@@ -867,6 +889,7 @@
       <c r="I9" s="4"/>
       <c r="J9" s="4"/>
       <c r="K9" s="4"/>
+      <c r="L9" s="4"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4"/>
@@ -880,6 +903,7 @@
       <c r="I10" s="4"/>
       <c r="J10" s="4"/>
       <c r="K10" s="4"/>
+      <c r="L10" s="4"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4"/>
@@ -893,6 +917,7 @@
       <c r="I11" s="4"/>
       <c r="J11" s="4"/>
       <c r="K11" s="4"/>
+      <c r="L11" s="4"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4"/>
@@ -906,6 +931,7 @@
       <c r="I12" s="4"/>
       <c r="J12" s="4"/>
       <c r="K12" s="4"/>
+      <c r="L12" s="4"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4"/>
@@ -919,6 +945,7 @@
       <c r="I13" s="4"/>
       <c r="J13" s="4"/>
       <c r="K13" s="4"/>
+      <c r="L13" s="4"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4"/>
@@ -932,6 +959,7 @@
       <c r="I14" s="4"/>
       <c r="J14" s="4"/>
       <c r="K14" s="4"/>
+      <c r="L14" s="4"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4"/>
@@ -945,6 +973,7 @@
       <c r="I15" s="4"/>
       <c r="J15" s="4"/>
       <c r="K15" s="4"/>
+      <c r="L15" s="4"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4"/>
@@ -958,6 +987,7 @@
       <c r="I16" s="4"/>
       <c r="J16" s="4"/>
       <c r="K16" s="4"/>
+      <c r="L16" s="4"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4"/>
@@ -971,6 +1001,7 @@
       <c r="I17" s="4"/>
       <c r="J17" s="4"/>
       <c r="K17" s="4"/>
+      <c r="L17" s="4"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4"/>
@@ -984,6 +1015,7 @@
       <c r="I18" s="4"/>
       <c r="J18" s="4"/>
       <c r="K18" s="4"/>
+      <c r="L18" s="4"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4"/>
@@ -997,6 +1029,7 @@
       <c r="I19" s="4"/>
       <c r="J19" s="4"/>
       <c r="K19" s="4"/>
+      <c r="L19" s="4"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4"/>
@@ -1010,6 +1043,7 @@
       <c r="I20" s="4"/>
       <c r="J20" s="4"/>
       <c r="K20" s="4"/>
+      <c r="L20" s="4"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4"/>
@@ -1023,6 +1057,7 @@
       <c r="I21" s="4"/>
       <c r="J21" s="4"/>
       <c r="K21" s="4"/>
+      <c r="L21" s="4"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="4"/>
@@ -1036,6 +1071,7 @@
       <c r="I22" s="4"/>
       <c r="J22" s="4"/>
       <c r="K22" s="4"/>
+      <c r="L22" s="4"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4"/>
@@ -1049,6 +1085,7 @@
       <c r="I23" s="4"/>
       <c r="J23" s="4"/>
       <c r="K23" s="4"/>
+      <c r="L23" s="4"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="4"/>
@@ -1062,6 +1099,7 @@
       <c r="I24" s="4"/>
       <c r="J24" s="4"/>
       <c r="K24" s="4"/>
+      <c r="L24" s="4"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4"/>
@@ -1075,6 +1113,7 @@
       <c r="I25" s="4"/>
       <c r="J25" s="4"/>
       <c r="K25" s="4"/>
+      <c r="L25" s="4"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="4"/>
@@ -1088,6 +1127,7 @@
       <c r="I26" s="4"/>
       <c r="J26" s="4"/>
       <c r="K26" s="4"/>
+      <c r="L26" s="4"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="4"/>
@@ -1101,6 +1141,7 @@
       <c r="I27" s="4"/>
       <c r="J27" s="4"/>
       <c r="K27" s="4"/>
+      <c r="L27" s="4"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="4"/>
@@ -1114,6 +1155,7 @@
       <c r="I28" s="4"/>
       <c r="J28" s="4"/>
       <c r="K28" s="4"/>
+      <c r="L28" s="4"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="4"/>
@@ -1127,6 +1169,7 @@
       <c r="I29" s="4"/>
       <c r="J29" s="4"/>
       <c r="K29" s="4"/>
+      <c r="L29" s="4"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="4"/>
@@ -1140,6 +1183,7 @@
       <c r="I30" s="4"/>
       <c r="J30" s="4"/>
       <c r="K30" s="4"/>
+      <c r="L30" s="4"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="4"/>
@@ -1153,6 +1197,7 @@
       <c r="I31" s="4"/>
       <c r="J31" s="4"/>
       <c r="K31" s="4"/>
+      <c r="L31" s="4"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="4"/>
@@ -1166,6 +1211,7 @@
       <c r="I32" s="4"/>
       <c r="J32" s="4"/>
       <c r="K32" s="4"/>
+      <c r="L32" s="4"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="4"/>
@@ -1179,6 +1225,7 @@
       <c r="I33" s="4"/>
       <c r="J33" s="4"/>
       <c r="K33" s="4"/>
+      <c r="L33" s="4"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4"/>
@@ -1192,6 +1239,7 @@
       <c r="I34" s="4"/>
       <c r="J34" s="4"/>
       <c r="K34" s="4"/>
+      <c r="L34" s="4"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="4"/>
@@ -1205,6 +1253,7 @@
       <c r="I35" s="4"/>
       <c r="J35" s="4"/>
       <c r="K35" s="4"/>
+      <c r="L35" s="4"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="4"/>
@@ -1218,6 +1267,7 @@
       <c r="I36" s="4"/>
       <c r="J36" s="4"/>
       <c r="K36" s="4"/>
+      <c r="L36" s="4"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="4"/>
@@ -1231,6 +1281,7 @@
       <c r="I37" s="4"/>
       <c r="J37" s="4"/>
       <c r="K37" s="4"/>
+      <c r="L37" s="4"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="4"/>
@@ -1244,6 +1295,7 @@
       <c r="I38" s="4"/>
       <c r="J38" s="4"/>
       <c r="K38" s="4"/>
+      <c r="L38" s="4"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="4"/>
@@ -1257,6 +1309,7 @@
       <c r="I39" s="4"/>
       <c r="J39" s="4"/>
       <c r="K39" s="4"/>
+      <c r="L39" s="4"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="4"/>
@@ -1270,6 +1323,7 @@
       <c r="I40" s="4"/>
       <c r="J40" s="4"/>
       <c r="K40" s="4"/>
+      <c r="L40" s="4"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="4"/>
@@ -1283,6 +1337,7 @@
       <c r="I41" s="4"/>
       <c r="J41" s="4"/>
       <c r="K41" s="4"/>
+      <c r="L41" s="4"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="4"/>
@@ -1296,6 +1351,7 @@
       <c r="I42" s="4"/>
       <c r="J42" s="4"/>
       <c r="K42" s="4"/>
+      <c r="L42" s="4"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="4"/>
@@ -1309,6 +1365,7 @@
       <c r="I43" s="4"/>
       <c r="J43" s="4"/>
       <c r="K43" s="4"/>
+      <c r="L43" s="4"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="4"/>
@@ -1322,6 +1379,7 @@
       <c r="I44" s="4"/>
       <c r="J44" s="4"/>
       <c r="K44" s="4"/>
+      <c r="L44" s="4"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="4"/>
@@ -1335,6 +1393,7 @@
       <c r="I45" s="4"/>
       <c r="J45" s="4"/>
       <c r="K45" s="4"/>
+      <c r="L45" s="4"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="4"/>
@@ -1348,6 +1407,7 @@
       <c r="I46" s="4"/>
       <c r="J46" s="4"/>
       <c r="K46" s="4"/>
+      <c r="L46" s="4"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -1494,6 +1554,14 @@
         <v>46</v>
       </c>
     </row>
+    <row r="16" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>50</v>
+      </c>
+    </row>
     <row r="17" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="10" t="s">
         <v>47</v>

--- a/templates/training_plan_template.xlsx
+++ b/templates/training_plan_template.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="56">
   <si>
     <t xml:space="preserve">Week</t>
   </si>
@@ -161,10 +161,10 @@
     <t xml:space="preserve">Any free-text note — cues, tempo, form reminders. Imported into the exercise's description field.</t>
   </si>
   <si>
-    <t xml:space="preserve">Optional link to a demonstration video (e.g. YouTube, MuscleWiki). Imported as a link, not embedded.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Note: a photo CAN come along with this template via the 'Picture' column above — but only when you zip this spreadsheet together with the image files it names and import using 'From spreadsheet + pictures (.zip)' (Plans &gt; New plan). A plain .csv/.xlsx import by itself can't carry the image, since a spreadsheet cell can only hold text. Video URL remains a link only, not an embedded file. Session logs and progress history live only in the app itself.</t>
+    <t xml:space="preserve">Optional link to a demonstration video (e.g. YouTube, MuscleWiki). Shown as a link by default; can be shown as an embedded player instead if you turn on the Embedding column for that row (YouTube links only).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Note: a photo CAN come along with this template via the 'Picture' column above - but only when you zip this spreadsheet together with the image files it names and import using 'From spreadsheet + pictures (.zip)' (Plans &gt; New plan). A plain .csv/.xlsx import by itself can't carry the image, since a spreadsheet cell can only hold text. A Video URL is shown as a link by default, or embedded if you turn on that row's Embedding column (YouTube links only) - see the Embedding row above. Session logs and progress history live only in the app itself.</t>
   </si>
   <si>
     <t xml:space="preserve">Picture</t>
@@ -174,6 +174,23 @@
   </si>
   <si>
     <t xml:space="preserve">Optional filename of a photo for this exercise, e.g. 'bench_press.jpg'. Only works when importing via 'From spreadsheet + pictures (.zip)' — zip this spreadsheet together with the image files it names (using exactly these filenames; folder structure inside the zip doesn't matter) and import that zip instead of the plain spreadsheet. The photo attaches to the resulting exercise. Leave blank for rows that don't need one.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Embedding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">yes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">yes/y/1/true (case-insensitive) turns on embedded playback for this row's Video URL, if it's a YouTube link - leave blank (or anything else) for no. Turning this on is your confirmation that you have the right to embed that specific video. If you share this plan with embedding turned on, you're responsible for that - the app doesn't review plan content, it only provides the platform. See the app's Disclaimer (Settings &gt; About) for the full policy.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Using AI to convert your own plan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">If you already have a training plan written down somewhere (a document, notes app, old spreadsheet, or just in your head), you can ask an AI assistant to fill in this template for you instead of doing it by hand. Attach this file to your AI assistant of choice and adapt this prompt:
+"I'm attaching a spreadsheet template for a workout-tracking app. Fill in the 'Plan' tab using the training plan I describe below, following the 'Instructions' tab's column definitions exactly. Keep one row per exercise-in-session; group rows into one session using matching Week + Day + Session Name; number 'Order' sequentially within each session starting at 1. Leave the 'Embedding' column blank unless I specifically tell you a video should be embedded, and never invent a video link yourself. Don't guess or invent values for any column I haven't given you information for - leave those cells blank instead. Return the completed spreadsheet in the same column order as the template.
+[describe your plan here, or paste your existing notes]"</t>
   </si>
 </sst>
 </file>
@@ -624,7 +641,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L46"/>
+  <dimension ref="A1:M46"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="7"/>
@@ -639,6 +656,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="28"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="32"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -678,6 +696,9 @@
       <c r="L1" s="1" t="s">
         <v>48</v>
       </c>
+      <c r="M1" s="1" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="n">
@@ -748,6 +769,9 @@
         <v>19</v>
       </c>
       <c r="L3" s="3"/>
+      <c r="M3" s="2" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="n">
@@ -862,6 +886,7 @@
       <c r="J7" s="4"/>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
+      <c r="M7" s="4"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4"/>
@@ -876,6 +901,7 @@
       <c r="J8" s="4"/>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
+      <c r="M8" s="4"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4"/>
@@ -890,6 +916,7 @@
       <c r="J9" s="4"/>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
+      <c r="M9" s="4"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4"/>
@@ -904,6 +931,7 @@
       <c r="J10" s="4"/>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
+      <c r="M10" s="4"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4"/>
@@ -918,6 +946,7 @@
       <c r="J11" s="4"/>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
+      <c r="M11" s="4"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4"/>
@@ -932,6 +961,7 @@
       <c r="J12" s="4"/>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
+      <c r="M12" s="4"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4"/>
@@ -946,6 +976,7 @@
       <c r="J13" s="4"/>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
+      <c r="M13" s="4"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4"/>
@@ -960,6 +991,7 @@
       <c r="J14" s="4"/>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
+      <c r="M14" s="4"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4"/>
@@ -974,6 +1006,7 @@
       <c r="J15" s="4"/>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
+      <c r="M15" s="4"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4"/>
@@ -988,6 +1021,7 @@
       <c r="J16" s="4"/>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
+      <c r="M16" s="4"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4"/>
@@ -1002,6 +1036,7 @@
       <c r="J17" s="4"/>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
+      <c r="M17" s="4"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4"/>
@@ -1016,6 +1051,7 @@
       <c r="J18" s="4"/>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
+      <c r="M18" s="4"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4"/>
@@ -1030,6 +1066,7 @@
       <c r="J19" s="4"/>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
+      <c r="M19" s="4"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4"/>
@@ -1044,6 +1081,7 @@
       <c r="J20" s="4"/>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
+      <c r="M20" s="4"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4"/>
@@ -1058,6 +1096,7 @@
       <c r="J21" s="4"/>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
+      <c r="M21" s="4"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="4"/>
@@ -1072,6 +1111,7 @@
       <c r="J22" s="4"/>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
+      <c r="M22" s="4"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4"/>
@@ -1086,6 +1126,7 @@
       <c r="J23" s="4"/>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
+      <c r="M23" s="4"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="4"/>
@@ -1100,6 +1141,7 @@
       <c r="J24" s="4"/>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
+      <c r="M24" s="4"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4"/>
@@ -1114,6 +1156,7 @@
       <c r="J25" s="4"/>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
+      <c r="M25" s="4"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="4"/>
@@ -1128,6 +1171,7 @@
       <c r="J26" s="4"/>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
+      <c r="M26" s="4"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="4"/>
@@ -1142,6 +1186,7 @@
       <c r="J27" s="4"/>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
+      <c r="M27" s="4"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="4"/>
@@ -1156,6 +1201,7 @@
       <c r="J28" s="4"/>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
+      <c r="M28" s="4"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="4"/>
@@ -1170,6 +1216,7 @@
       <c r="J29" s="4"/>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
+      <c r="M29" s="4"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="4"/>
@@ -1184,6 +1231,7 @@
       <c r="J30" s="4"/>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
+      <c r="M30" s="4"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="4"/>
@@ -1198,6 +1246,7 @@
       <c r="J31" s="4"/>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
+      <c r="M31" s="4"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="4"/>
@@ -1212,6 +1261,7 @@
       <c r="J32" s="4"/>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
+      <c r="M32" s="4"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="4"/>
@@ -1226,6 +1276,7 @@
       <c r="J33" s="4"/>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
+      <c r="M33" s="4"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4"/>
@@ -1240,6 +1291,7 @@
       <c r="J34" s="4"/>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
+      <c r="M34" s="4"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="4"/>
@@ -1254,6 +1306,7 @@
       <c r="J35" s="4"/>
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
+      <c r="M35" s="4"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="4"/>
@@ -1268,6 +1321,7 @@
       <c r="J36" s="4"/>
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
+      <c r="M36" s="4"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="4"/>
@@ -1282,6 +1336,7 @@
       <c r="J37" s="4"/>
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
+      <c r="M37" s="4"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="4"/>
@@ -1296,6 +1351,7 @@
       <c r="J38" s="4"/>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
+      <c r="M38" s="4"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="4"/>
@@ -1310,6 +1366,7 @@
       <c r="J39" s="4"/>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
+      <c r="M39" s="4"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="4"/>
@@ -1324,6 +1381,7 @@
       <c r="J40" s="4"/>
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
+      <c r="M40" s="4"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="4"/>
@@ -1338,6 +1396,7 @@
       <c r="J41" s="4"/>
       <c r="K41" s="4"/>
       <c r="L41" s="4"/>
+      <c r="M41" s="4"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="4"/>
@@ -1352,6 +1411,7 @@
       <c r="J42" s="4"/>
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
+      <c r="M42" s="4"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="4"/>
@@ -1366,6 +1426,7 @@
       <c r="J43" s="4"/>
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
+      <c r="M43" s="4"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="4"/>
@@ -1380,6 +1441,7 @@
       <c r="J44" s="4"/>
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
+      <c r="M44" s="4"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="4"/>
@@ -1394,6 +1456,7 @@
       <c r="J45" s="4"/>
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
+      <c r="M45" s="4"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="4"/>
@@ -1408,6 +1471,7 @@
       <c r="J46" s="4"/>
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
+      <c r="M46" s="4"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -1439,7 +1503,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20"/>
@@ -1568,11 +1632,33 @@
       </c>
       <c r="B17" s="10"/>
     </row>
+    <row r="18" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B19" s="5"/>
+    </row>
+    <row r="20" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B20" s="6"/>
+    </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="5">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A20:B20"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/templates/training_plan_template.xlsx
+++ b/templates/training_plan_template.xlsx
@@ -152,7 +152,7 @@
     <t xml:space="preserve">Reps per set. Free text, since ranges (e.g. '8-10') and text like 'AMRAP' or 'to failure' are both valid.</t>
   </si>
   <si>
-    <t xml:space="preserve">Free text — e.g. '60kg', '135lb', 'RPE 8', '70% 1RM'. The app does not assume a single unit or scale.</t>
+    <t xml:space="preserve">Free text - e.g. '60kg', '135lb', 'RPE 8', '70% 1RM'. The app does not assume a single unit or scale. For a bodyweight or band-resisted exercise, leave this blank or use whatever you'd actually write down - 'Bodyweight', a band color ('Red band'), or a resistance level all work just as well as a number; the app never requires a weight figure here.</t>
   </si>
   <si>
     <t xml:space="preserve">Rest between sets, in seconds, as a whole number.</t>

--- a/templates/training_plan_template.xlsx
+++ b/templates/training_plan_template.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="59">
   <si>
     <t xml:space="preserve">Week</t>
   </si>
@@ -189,8 +189,17 @@
   </si>
   <si>
     <t xml:space="preserve">If you already have a training plan written down somewhere (a document, notes app, old spreadsheet, or just in your head), you can ask an AI assistant to fill in this template for you instead of doing it by hand. Attach this file to your AI assistant of choice and adapt this prompt:
-"I'm attaching a spreadsheet template for a workout-tracking app. Fill in the 'Plan' tab using the training plan I describe below, following the 'Instructions' tab's column definitions exactly. Keep one row per exercise-in-session; group rows into one session using matching Week + Day + Session Name; number 'Order' sequentially within each session starting at 1. Leave the 'Embedding' column blank unless I specifically tell you a video should be embedded, and never invent a video link yourself. Don't guess or invent values for any column I haven't given you information for - leave those cells blank instead. Return the completed spreadsheet in the same column order as the template.
+"I'm attaching a spreadsheet template for a workout-tracking app. Fill in the 'Plan' tab using the training plan I describe below, following the 'Instructions' tab's column definitions exactly. Keep one row per exercise-in-session; group rows into one session using matching Week + Day + Session Name; number 'Order' sequentially within each session starting at 1. Leave the 'Embedding' column blank unless I specifically tell you a video should be embedded, and never invent a video link yourself. Fill in 'Created By' only if I tell you this plan is from a specific trainer/coach, with their name exactly as I give it to you. Don't guess or invent values for any column I haven't given you information for - leave those cells blank instead. Return the completed spreadsheet in the same column order as the template.
 [describe your plan here, or paste your existing notes]"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Created By</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jane Trainer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optional - the trainer's name, if this plan was built by one for a client. Shown in the trainer-facing PDF report's header when every session in the exported date range traces back to a plan with this set. Leave blank for a plan you built for yourself.</t>
   </si>
 </sst>
 </file>
@@ -641,7 +650,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M46"/>
+  <dimension ref="A1:N46"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="7"/>
@@ -657,6 +666,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="32"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="24"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="20"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -699,6 +709,9 @@
       <c r="M1" s="1" t="s">
         <v>51</v>
       </c>
+      <c r="N1" s="1" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="n">
@@ -734,6 +747,9 @@
       <c r="K2" s="3"/>
       <c r="L2" s="3" t="s">
         <v>49</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -887,6 +903,7 @@
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
       <c r="M7" s="4"/>
+      <c r="N7" s="4"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4"/>
@@ -902,6 +919,7 @@
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
       <c r="M8" s="4"/>
+      <c r="N8" s="4"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4"/>
@@ -917,6 +935,7 @@
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
       <c r="M9" s="4"/>
+      <c r="N9" s="4"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4"/>
@@ -932,6 +951,7 @@
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
       <c r="M10" s="4"/>
+      <c r="N10" s="4"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4"/>
@@ -947,6 +967,7 @@
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
       <c r="M11" s="4"/>
+      <c r="N11" s="4"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4"/>
@@ -962,6 +983,7 @@
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
       <c r="M12" s="4"/>
+      <c r="N12" s="4"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4"/>
@@ -977,6 +999,7 @@
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
       <c r="M13" s="4"/>
+      <c r="N13" s="4"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4"/>
@@ -992,6 +1015,7 @@
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
       <c r="M14" s="4"/>
+      <c r="N14" s="4"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4"/>
@@ -1007,6 +1031,7 @@
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
       <c r="M15" s="4"/>
+      <c r="N15" s="4"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4"/>
@@ -1022,6 +1047,7 @@
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
       <c r="M16" s="4"/>
+      <c r="N16" s="4"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4"/>
@@ -1037,6 +1063,7 @@
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
       <c r="M17" s="4"/>
+      <c r="N17" s="4"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4"/>
@@ -1052,6 +1079,7 @@
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
       <c r="M18" s="4"/>
+      <c r="N18" s="4"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4"/>
@@ -1067,6 +1095,7 @@
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
       <c r="M19" s="4"/>
+      <c r="N19" s="4"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4"/>
@@ -1082,6 +1111,7 @@
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
       <c r="M20" s="4"/>
+      <c r="N20" s="4"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4"/>
@@ -1097,6 +1127,7 @@
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
       <c r="M21" s="4"/>
+      <c r="N21" s="4"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="4"/>
@@ -1112,6 +1143,7 @@
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
       <c r="M22" s="4"/>
+      <c r="N22" s="4"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4"/>
@@ -1127,6 +1159,7 @@
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
       <c r="M23" s="4"/>
+      <c r="N23" s="4"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="4"/>
@@ -1142,6 +1175,7 @@
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
       <c r="M24" s="4"/>
+      <c r="N24" s="4"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4"/>
@@ -1157,6 +1191,7 @@
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
       <c r="M25" s="4"/>
+      <c r="N25" s="4"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="4"/>
@@ -1172,6 +1207,7 @@
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
       <c r="M26" s="4"/>
+      <c r="N26" s="4"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="4"/>
@@ -1187,6 +1223,7 @@
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
       <c r="M27" s="4"/>
+      <c r="N27" s="4"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="4"/>
@@ -1202,6 +1239,7 @@
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
       <c r="M28" s="4"/>
+      <c r="N28" s="4"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="4"/>
@@ -1217,6 +1255,7 @@
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
       <c r="M29" s="4"/>
+      <c r="N29" s="4"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="4"/>
@@ -1232,6 +1271,7 @@
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
       <c r="M30" s="4"/>
+      <c r="N30" s="4"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="4"/>
@@ -1247,6 +1287,7 @@
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
       <c r="M31" s="4"/>
+      <c r="N31" s="4"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="4"/>
@@ -1262,6 +1303,7 @@
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
       <c r="M32" s="4"/>
+      <c r="N32" s="4"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="4"/>
@@ -1277,6 +1319,7 @@
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
       <c r="M33" s="4"/>
+      <c r="N33" s="4"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4"/>
@@ -1292,6 +1335,7 @@
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
       <c r="M34" s="4"/>
+      <c r="N34" s="4"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="4"/>
@@ -1307,6 +1351,7 @@
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
       <c r="M35" s="4"/>
+      <c r="N35" s="4"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="4"/>
@@ -1322,6 +1367,7 @@
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
       <c r="M36" s="4"/>
+      <c r="N36" s="4"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="4"/>
@@ -1337,6 +1383,7 @@
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
       <c r="M37" s="4"/>
+      <c r="N37" s="4"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="4"/>
@@ -1352,6 +1399,7 @@
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
       <c r="M38" s="4"/>
+      <c r="N38" s="4"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="4"/>
@@ -1367,6 +1415,7 @@
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
       <c r="M39" s="4"/>
+      <c r="N39" s="4"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="4"/>
@@ -1382,6 +1431,7 @@
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
       <c r="M40" s="4"/>
+      <c r="N40" s="4"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="4"/>
@@ -1397,6 +1447,7 @@
       <c r="K41" s="4"/>
       <c r="L41" s="4"/>
       <c r="M41" s="4"/>
+      <c r="N41" s="4"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="4"/>
@@ -1412,6 +1463,7 @@
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
       <c r="M42" s="4"/>
+      <c r="N42" s="4"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="4"/>
@@ -1427,6 +1479,7 @@
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
       <c r="M43" s="4"/>
+      <c r="N43" s="4"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="4"/>
@@ -1442,6 +1495,7 @@
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
       <c r="M44" s="4"/>
+      <c r="N44" s="4"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="4"/>
@@ -1457,6 +1511,7 @@
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
       <c r="M45" s="4"/>
+      <c r="N45" s="4"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="4"/>
@@ -1472,6 +1527,7 @@
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
       <c r="M46" s="4"/>
+      <c r="N46" s="4"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -1503,7 +1559,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20"/>
@@ -1640,24 +1696,32 @@
         <v>53</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="5" t="s">
+    <row r="19" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="B19" s="5"/>
-    </row>
-    <row r="20" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="6" t="s">
+      <c r="B20" s="5"/>
+    </row>
+    <row r="21" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="B20" s="6"/>
+      <c r="B21" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A21:B21"/>
     <mergeCell ref="A20:B20"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
